--- a/data/trans_dic/P64D$noloshace_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,03</t>
+          <t>0,0; 25,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,71</t>
+          <t>0,0; 13,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 15,55</t>
+          <t>1,79; 15,83</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 10,18</t>
+          <t>3,46; 10,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,31</t>
+          <t>1,05; 5,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,98</t>
+          <t>2,82; 7,05</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,27</t>
+          <t>2,4; 6,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,82</t>
+          <t>1,98; 5,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,02</t>
+          <t>2,53; 5,02</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,49</t>
+          <t>0,55; 3,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,09</t>
+          <t>2,29; 5,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,64</t>
+          <t>1,2; 3,62</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,28</t>
+          <t>2,0; 6,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,4</t>
+          <t>3,67; 8,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,21</t>
+          <t>3,19; 6,25</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,86</t>
+          <t>0,0; 24,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 14,43</t>
+          <t>1,21; 14,9</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,97</t>
+          <t>2,47; 5,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,53</t>
+          <t>2,74; 4,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,44</t>
+          <t>2,78; 4,44</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 24491</t>
+          <t>0; 22707</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 11140</t>
+          <t>0; 11204</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3010; 26715</t>
+          <t>3074; 27205</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12508; 35669</t>
+          <t>12137; 38292</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3704; 18565</t>
+          <t>3662; 19141</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19368; 48846</t>
+          <t>19743; 49350</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10870; 28984</t>
+          <t>11106; 28812</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6500; 16915</t>
+          <t>6953; 17801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20125; 40805</t>
+          <t>20561; 40824</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4685; 26000</t>
+          <t>4063; 26482</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9751; 23070</t>
+          <t>10387; 23529</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14215; 43654</t>
+          <t>14362; 43321</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6338; 18790</t>
+          <t>5986; 18400</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7521; 17484</t>
+          <t>7629; 17389</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15955; 31494</t>
+          <t>16206; 31697</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4382</t>
+          <t>0; 4086</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>420; 5007</t>
+          <t>421; 5170</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48000; 97633</t>
+          <t>48465; 99132</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38912; 66157</t>
+          <t>40003; 66794</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>96243; 151993</t>
+          <t>95297; 152098</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$noloshace_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,06</t>
+          <t>0,0; 13,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,79</t>
+          <t>0,0; 12,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,83</t>
+          <t>0,87; 9,62</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,93</t>
+          <t>3,38; 9,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,47</t>
+          <t>1,64; 5,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,05</t>
+          <t>3,34; 7,72</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,24</t>
+          <t>2,67; 6,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,07</t>
+          <t>2,21; 5,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,02</t>
+          <t>2,92; 5,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,55</t>
+          <t>1,63; 4,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,2</t>
+          <t>2,84; 5,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,62</t>
+          <t>2,55; 4,66</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,15</t>
+          <t>3,23; 8,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,35</t>
+          <t>4,17; 9,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,25</t>
+          <t>4,0; 7,56</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,12</t>
+          <t>0,0; 26,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,11</t>
+          <t>0,0; 9,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 14,9</t>
+          <t>1,12; 13,29</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,04</t>
+          <t>3,48; 5,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,57</t>
+          <t>3,27; 5,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,44</t>
+          <t>3,67; 5,15</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>7549</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 22707</t>
+          <t>0; 14316</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 11204</t>
+          <t>0; 11603</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3074; 27205</t>
+          <t>1719; 18917</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31976</t>
+          <t>35809</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12137; 38292</t>
+          <t>13381; 38970</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3662; 19141</t>
+          <t>5162; 18857</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19743; 49350</t>
+          <t>23718; 54927</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>37433</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11106; 28812</t>
+          <t>14311; 37234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6953; 17801</t>
+          <t>8792; 20985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20561; 40824</t>
+          <t>27304; 51597</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>34753</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4063; 26482</t>
+          <t>8869; 25667</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10387; 23529</t>
+          <t>12914; 26342</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14362; 43321</t>
+          <t>25469; 46549</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>31391</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5986; 18400</t>
+          <t>10571; 26312</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7629; 17389</t>
+          <t>9707; 21783</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16206; 31697</t>
+          <t>22391; 42321</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>432</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1918</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4086</t>
+          <t>0; 5014</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2149</t>
+          <t>0; 1791</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>421; 5170</t>
+          <t>437; 5166</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48465; 99132</t>
+          <t>67045; 108552</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>40003; 66794</t>
+          <t>49386; 77749</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>95297; 152098</t>
+          <t>126351; 177170</t>
         </is>
       </c>
     </row>
